--- a/Data/Input/Emails_Local.xlsx
+++ b/Data/Input/Emails_Local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Jobs &amp; Email\Mail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06AAAEFA-ED94-4E0C-B4D4-9437204F977E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5193BA0-8FA5-4550-A2CF-75EC5014068F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="53">
   <si>
     <t>duongduy12318@gmail.com</t>
   </si>
@@ -203,6 +203,9 @@
   </si>
   <si>
     <t>thanhduykx@gmail.com</t>
+  </si>
+  <si>
+    <t>abcd@fpt.edu.com</t>
   </si>
 </sst>
 </file>
@@ -698,6 +701,9 @@
       <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
+      <c r="E8" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F8" s="6">
         <v>45860</v>
       </c>
@@ -715,6 +721,9 @@
       <c r="D9" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="E9" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F9" s="6">
         <v>45860</v>
       </c>
@@ -732,6 +741,9 @@
       <c r="D10" s="4" t="s">
         <v>31</v>
       </c>
+      <c r="E10" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F10" s="6">
         <v>45861</v>
       </c>
@@ -749,6 +761,9 @@
       <c r="D11" s="4" t="s">
         <v>32</v>
       </c>
+      <c r="E11" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F11" s="6">
         <v>45861</v>
       </c>
@@ -766,6 +781,9 @@
       <c r="D12" s="4" t="s">
         <v>33</v>
       </c>
+      <c r="E12" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F12" s="6">
         <v>45861</v>
       </c>
@@ -783,6 +801,9 @@
       <c r="D13" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="E13" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F13" s="6">
         <v>45861</v>
       </c>
@@ -800,6 +821,9 @@
       <c r="D14" s="4" t="s">
         <v>35</v>
       </c>
+      <c r="E14" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F14" s="6">
         <v>45861</v>
       </c>
@@ -817,6 +841,9 @@
       <c r="D15" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="E15" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F15" s="6">
         <v>45862</v>
       </c>
@@ -834,6 +861,9 @@
       <c r="D16" s="4" t="s">
         <v>37</v>
       </c>
+      <c r="E16" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F16" s="6">
         <v>45862</v>
       </c>
@@ -851,6 +881,9 @@
       <c r="D17" s="4" t="s">
         <v>38</v>
       </c>
+      <c r="E17" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F17" s="6">
         <v>45862</v>
       </c>
@@ -868,6 +901,9 @@
       <c r="D18" s="4" t="s">
         <v>39</v>
       </c>
+      <c r="E18" s="10" t="s">
+        <v>52</v>
+      </c>
       <c r="F18" s="6">
         <v>45862</v>
       </c>
@@ -884,6 +920,9 @@
       </c>
       <c r="D19" s="4" t="s">
         <v>40</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="F19" s="6">
         <v>45863</v>
@@ -1898,8 +1937,10 @@
     <hyperlink ref="E6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="E7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="E5" r:id="rId5" xr:uid="{0B539A5E-85B9-47BD-A2A3-B90FD6698075}"/>
+    <hyperlink ref="E8" r:id="rId6" xr:uid="{352771BC-8266-40B9-B326-7331AE90C796}"/>
+    <hyperlink ref="E9:E19" r:id="rId7" display="abcd@fpt.edu.com" xr:uid="{C94870CB-1F7E-4D39-A72C-3F9B8CDE1266}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId6"/>
+  <pageSetup orientation="landscape" r:id="rId8"/>
 </worksheet>
 </file>
--- a/Data/Input/Emails_Local.xlsx
+++ b/Data/Input/Emails_Local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Jobs &amp; Email\Mail\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9485C49D-C1FF-4E85-8864-919FE285D511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2F649F-A3E4-4439-97A6-927D2F1A729C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>duongduy12318@gmail.com</t>
   </si>
@@ -69,24 +69,6 @@
     <t>Jayvee</t>
   </si>
   <si>
-    <t>Annfrei</t>
-  </si>
-  <si>
-    <t>Berlin</t>
-  </si>
-  <si>
-    <t>Joselito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MERIGINE </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Joshua </t>
-  </si>
-  <si>
-    <t>Mark</t>
-  </si>
-  <si>
     <t>CONTACT NUMBER</t>
   </si>
   <si>
@@ -106,42 +88,6 @@
   </si>
   <si>
     <t>09150000006</t>
-  </si>
-  <si>
-    <t>09150000020</t>
-  </si>
-  <si>
-    <t>09150000021</t>
-  </si>
-  <si>
-    <t>09150000022</t>
-  </si>
-  <si>
-    <t>09150000023</t>
-  </si>
-  <si>
-    <t>09150000024</t>
-  </si>
-  <si>
-    <t>09150000025</t>
-  </si>
-  <si>
-    <t>09150000026</t>
-  </si>
-  <si>
-    <t>09150000027</t>
-  </si>
-  <si>
-    <t>09150000028</t>
-  </si>
-  <si>
-    <t>09150000029</t>
-  </si>
-  <si>
-    <t>09150000030</t>
-  </si>
-  <si>
-    <t>09150000031</t>
   </si>
   <si>
     <r>
@@ -184,9 +130,6 @@
   </si>
   <si>
     <t>thanhduykx@gmail.com</t>
-  </si>
-  <si>
-    <t>abcd@fpt.edu.com</t>
   </si>
   <si>
     <t>Employee
@@ -534,30 +477,30 @@
   <sheetData>
     <row r="1" spans="1:5" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>0</v>
@@ -568,13 +511,13 @@
     </row>
     <row r="3" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>6</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>1</v>
@@ -585,13 +528,13 @@
     </row>
     <row r="4" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>2</v>
@@ -602,16 +545,16 @@
     </row>
     <row r="5" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>8</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E5" s="6">
         <v>45856</v>
@@ -619,13 +562,13 @@
     </row>
     <row r="6" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>3</v>
@@ -636,13 +579,13 @@
     </row>
     <row r="7" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>10</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>4</v>
@@ -652,208 +595,76 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E8" s="6">
-        <v>45860</v>
-      </c>
+      <c r="A8" s="8"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="6"/>
     </row>
     <row r="9" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="6">
-        <v>45860</v>
-      </c>
+      <c r="A9" s="8"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="6"/>
     </row>
     <row r="10" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="6">
-        <v>45861</v>
-      </c>
+      <c r="A10" s="9"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="6">
-        <v>45861</v>
-      </c>
+      <c r="A11" s="9"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="6">
-        <v>45861</v>
-      </c>
+      <c r="A12" s="9"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="6"/>
     </row>
     <row r="13" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="6">
-        <v>45861</v>
-      </c>
+      <c r="A13" s="9"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="6">
-        <v>45861</v>
-      </c>
+      <c r="A14" s="8"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E15" s="6">
-        <v>45862</v>
-      </c>
+      <c r="A15" s="8"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E16" s="6">
-        <v>45862</v>
-      </c>
+      <c r="A16" s="9"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="6"/>
     </row>
     <row r="17" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="6">
-        <v>45862</v>
-      </c>
+      <c r="A17" s="9"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="6"/>
     </row>
     <row r="18" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="6">
-        <v>45862</v>
-      </c>
+      <c r="A18" s="9"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="6"/>
     </row>
     <row r="19" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="B19" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E19" s="6">
-        <v>45863</v>
-      </c>
+      <c r="A19" s="9"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9"/>
@@ -1864,10 +1675,8 @@
     <hyperlink ref="D6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="D7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="D5" r:id="rId5" xr:uid="{0B539A5E-85B9-47BD-A2A3-B90FD6698075}"/>
-    <hyperlink ref="D8" r:id="rId6" xr:uid="{352771BC-8266-40B9-B326-7331AE90C796}"/>
-    <hyperlink ref="D9:D19" r:id="rId7" display="abcd@fpt.edu.com" xr:uid="{C94870CB-1F7E-4D39-A72C-3F9B8CDE1266}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId8"/>
+  <pageSetup orientation="landscape" r:id="rId6"/>
 </worksheet>
 </file>